--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117972969</v>
+        <v>117972951</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>90510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,42 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871848</v>
+        <v>871766</v>
       </c>
       <c r="R6" t="n">
-        <v>7441438</v>
+        <v>7441445</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1170,18 +1166,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117972958</v>
+        <v>117972969</v>
       </c>
       <c r="B7" t="n">
-        <v>96797</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1202,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871865</v>
+        <v>871848</v>
       </c>
       <c r="R7" t="n">
-        <v>7441441</v>
+        <v>7441438</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1278,12 +1272,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117972951</v>
+        <v>117972958</v>
       </c>
       <c r="B8" t="n">
-        <v>90510</v>
+        <v>96797</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871766</v>
+        <v>871865</v>
       </c>
       <c r="R8" t="n">
-        <v>7441445</v>
+        <v>7441441</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117972946</v>
+        <v>117972979</v>
       </c>
       <c r="B15" t="n">
-        <v>90660</v>
+        <v>78480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>871898</v>
+        <v>871758</v>
       </c>
       <c r="R15" t="n">
-        <v>7441555</v>
+        <v>7441521</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117972979</v>
+        <v>117972946</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>90660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>871758</v>
+        <v>871898</v>
       </c>
       <c r="R16" t="n">
-        <v>7441521</v>
+        <v>7441555</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117972984</v>
+        <v>117972952</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,25 +3724,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>871806</v>
+        <v>871898</v>
       </c>
       <c r="R31" t="n">
-        <v>7441439</v>
+        <v>7441404</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117972952</v>
+        <v>117972984</v>
       </c>
       <c r="B32" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3826,25 +3826,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>871898</v>
+        <v>871806</v>
       </c>
       <c r="R32" t="n">
-        <v>7441404</v>
+        <v>7441439</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4237,10 +4237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117972954</v>
+        <v>117972968</v>
       </c>
       <c r="B36" t="n">
-        <v>97857</v>
+        <v>97836</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,25 +4249,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>871817</v>
+        <v>871809</v>
       </c>
       <c r="R36" t="n">
-        <v>7441499</v>
+        <v>7441501</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4313,6 +4313,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4339,10 +4344,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117972957</v>
+        <v>117972971</v>
       </c>
       <c r="B37" t="n">
-        <v>96797</v>
+        <v>97836</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4351,38 +4356,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>871810</v>
+        <v>871841</v>
       </c>
       <c r="R37" t="n">
-        <v>7441526</v>
+        <v>7441558</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4417,12 +4426,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4441,10 +4456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117972968</v>
+        <v>117972954</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4453,25 +4468,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,10 +4496,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>871809</v>
+        <v>871817</v>
       </c>
       <c r="R38" t="n">
-        <v>7441501</v>
+        <v>7441499</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4517,11 +4532,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4548,10 +4558,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117972971</v>
+        <v>117972957</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>96797</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,42 +4570,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>871841</v>
+        <v>871810</v>
       </c>
       <c r="R39" t="n">
-        <v>7441558</v>
+        <v>7441526</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4630,18 +4636,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5987,10 +5987,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117985305</v>
+        <v>117985319</v>
       </c>
       <c r="B53" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5999,25 +5999,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>871855</v>
+        <v>871677</v>
       </c>
       <c r="R53" t="n">
-        <v>7441426</v>
+        <v>7441539</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6089,10 +6089,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117985319</v>
+        <v>117985300</v>
       </c>
       <c r="B54" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6105,21 +6105,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>871677</v>
+        <v>871739</v>
       </c>
       <c r="R54" t="n">
-        <v>7441539</v>
+        <v>7441532</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6165,6 +6165,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6191,10 +6196,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117985300</v>
+        <v>117985305</v>
       </c>
       <c r="B55" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6203,25 +6208,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6231,10 +6236,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>871739</v>
+        <v>871855</v>
       </c>
       <c r="R55" t="n">
-        <v>7441532</v>
+        <v>7441426</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6267,11 +6272,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117972985</v>
+        <v>117972986</v>
       </c>
       <c r="B2" t="n">
         <v>78480</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871922</v>
+        <v>871918</v>
       </c>
       <c r="R2" t="n">
-        <v>7441513</v>
+        <v>7441530</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117972962</v>
+        <v>117972983</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871677</v>
+        <v>871793</v>
       </c>
       <c r="R3" t="n">
-        <v>7441598</v>
+        <v>7441442</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117972980</v>
+        <v>117972959</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>871849</v>
+        <v>871896</v>
       </c>
       <c r="R4" t="n">
-        <v>7441497</v>
+        <v>7441398</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117972947</v>
+        <v>117972961</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>871772</v>
+        <v>871700</v>
       </c>
       <c r="R5" t="n">
-        <v>7441436</v>
+        <v>7441551</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117972951</v>
+        <v>117972948</v>
       </c>
       <c r="B6" t="n">
-        <v>90510</v>
+        <v>56499</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871766</v>
+        <v>871922</v>
       </c>
       <c r="R6" t="n">
-        <v>7441445</v>
+        <v>7441417</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Höna med ungar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117972969</v>
+        <v>117972973</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1234,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871848</v>
+        <v>871659</v>
       </c>
       <c r="R7" t="n">
-        <v>7441438</v>
+        <v>7441583</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1274,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 kvm</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117972958</v>
+        <v>117972956</v>
       </c>
       <c r="B8" t="n">
         <v>96797</v>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871865</v>
+        <v>871802</v>
       </c>
       <c r="R8" t="n">
-        <v>7441441</v>
+        <v>7441495</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1404,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117972983</v>
+        <v>117972981</v>
       </c>
       <c r="B9" t="n">
         <v>78480</v>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>871793</v>
+        <v>871821</v>
       </c>
       <c r="R9" t="n">
-        <v>7441442</v>
+        <v>7441539</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117972965</v>
+        <v>117972977</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871700</v>
+        <v>871676</v>
       </c>
       <c r="R10" t="n">
-        <v>7441545</v>
+        <v>7441585</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1582,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117972970</v>
+        <v>117972985</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,42 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>871719</v>
+        <v>871922</v>
       </c>
       <c r="R11" t="n">
-        <v>7441553</v>
+        <v>7441513</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1695,18 +1696,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117972960</v>
+        <v>117972946</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>90660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,25 +1732,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>871899</v>
+        <v>871898</v>
       </c>
       <c r="R12" t="n">
-        <v>7441403</v>
+        <v>7441555</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1801,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117972977</v>
+        <v>117972968</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>871676</v>
+        <v>871809</v>
       </c>
       <c r="R13" t="n">
-        <v>7441585</v>
+        <v>7441501</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1908,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117972959</v>
+        <v>117972958</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>96797</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1941,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>871896</v>
+        <v>871865</v>
       </c>
       <c r="R14" t="n">
-        <v>7441398</v>
+        <v>7441441</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2010,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117972979</v>
+        <v>117972974</v>
       </c>
       <c r="B15" t="n">
         <v>78480</v>
@@ -2081,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>871758</v>
+        <v>871944</v>
       </c>
       <c r="R15" t="n">
-        <v>7441521</v>
+        <v>7441550</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2143,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117972946</v>
+        <v>117972980</v>
       </c>
       <c r="B16" t="n">
-        <v>90660</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>871898</v>
+        <v>871849</v>
       </c>
       <c r="R16" t="n">
-        <v>7441555</v>
+        <v>7441497</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2245,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117972964</v>
+        <v>117972962</v>
       </c>
       <c r="B17" t="n">
         <v>97836</v>
@@ -2285,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>871821</v>
+        <v>871677</v>
       </c>
       <c r="R17" t="n">
-        <v>7441503</v>
+        <v>7441598</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2325,7 +2315,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>25 kvm</t>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117972976</v>
+        <v>117972965</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,25 +2354,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>871824</v>
+        <v>871700</v>
       </c>
       <c r="R18" t="n">
-        <v>7441576</v>
+        <v>7441545</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2428,6 +2418,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117972948</v>
+        <v>117972979</v>
       </c>
       <c r="B19" t="n">
-        <v>56499</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,25 +2461,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>871922</v>
+        <v>871758</v>
       </c>
       <c r="R19" t="n">
-        <v>7441417</v>
+        <v>7441521</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2530,11 +2525,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Höna med ungar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,7 +2551,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117972982</v>
+        <v>117972984</v>
       </c>
       <c r="B20" t="n">
         <v>78480</v>
@@ -2601,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>871783</v>
+        <v>871806</v>
       </c>
       <c r="R20" t="n">
-        <v>7441488</v>
+        <v>7441439</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2663,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117972981</v>
+        <v>117972952</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,25 +2665,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>871821</v>
+        <v>871898</v>
       </c>
       <c r="R21" t="n">
-        <v>7441539</v>
+        <v>7441404</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2765,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117972966</v>
+        <v>117972949</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>56499</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,38 +2767,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>871759</v>
+        <v>871818</v>
       </c>
       <c r="R22" t="n">
-        <v>7441511</v>
+        <v>7441470</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2845,7 +2839,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2872,10 +2866,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117972975</v>
+        <v>117972966</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,25 +2878,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2906,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>871806</v>
+        <v>871759</v>
       </c>
       <c r="R23" t="n">
-        <v>7441478</v>
+        <v>7441511</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2948,6 +2942,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117972978</v>
+        <v>117972963</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2986,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>871672</v>
+        <v>871771</v>
       </c>
       <c r="R24" t="n">
-        <v>7441536</v>
+        <v>7441497</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3050,6 +3049,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,10 +3080,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117972973</v>
+        <v>117972947</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,42 +3092,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>871659</v>
+        <v>871772</v>
       </c>
       <c r="R25" t="n">
-        <v>7441583</v>
+        <v>7441436</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3158,18 +3158,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3290,7 +3284,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117972974</v>
+        <v>117972976</v>
       </c>
       <c r="B27" t="n">
         <v>78480</v>
@@ -3330,10 +3324,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>871944</v>
+        <v>871824</v>
       </c>
       <c r="R27" t="n">
-        <v>7441550</v>
+        <v>7441576</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3392,7 +3386,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117972961</v>
+        <v>117972964</v>
       </c>
       <c r="B28" t="n">
         <v>97836</v>
@@ -3432,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>871700</v>
+        <v>871821</v>
       </c>
       <c r="R28" t="n">
-        <v>7441551</v>
+        <v>7441503</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3472,7 +3466,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>4 kvm</t>
+          <t>25 kvm</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3499,10 +3493,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117972949</v>
+        <v>117972969</v>
       </c>
       <c r="B29" t="n">
-        <v>56499</v>
+        <v>97836</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3511,31 +3505,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3543,10 +3537,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>871818</v>
+        <v>871848</v>
       </c>
       <c r="R29" t="n">
-        <v>7441470</v>
+        <v>7441438</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3583,7 +3577,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3592,6 +3586,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3610,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117972986</v>
+        <v>117972957</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>96797</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3622,25 +3617,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>871918</v>
+        <v>871810</v>
       </c>
       <c r="R30" t="n">
-        <v>7441530</v>
+        <v>7441526</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3712,10 +3707,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117972952</v>
+        <v>117972970</v>
       </c>
       <c r="B31" t="n">
-        <v>97857</v>
+        <v>97836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,38 +3719,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>871898</v>
+        <v>871719</v>
       </c>
       <c r="R31" t="n">
-        <v>7441404</v>
+        <v>7441553</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3790,12 +3789,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3814,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117972984</v>
+        <v>117972960</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3826,25 +3831,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3854,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>871806</v>
+        <v>871899</v>
       </c>
       <c r="R32" t="n">
-        <v>7441439</v>
+        <v>7441403</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3890,6 +3895,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4028,10 +4038,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117972956</v>
+        <v>117972982</v>
       </c>
       <c r="B34" t="n">
-        <v>96797</v>
+        <v>78480</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,25 +4050,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4068,10 +4078,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>871802</v>
+        <v>871783</v>
       </c>
       <c r="R34" t="n">
-        <v>7441495</v>
+        <v>7441488</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4130,10 +4140,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117972963</v>
+        <v>117972978</v>
       </c>
       <c r="B35" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4142,25 +4152,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4170,10 +4180,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>871771</v>
+        <v>871672</v>
       </c>
       <c r="R35" t="n">
-        <v>7441497</v>
+        <v>7441536</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4206,11 +4216,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4237,10 +4242,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117972968</v>
+        <v>117972951</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>90510</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4249,25 +4254,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4277,10 +4282,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>871809</v>
+        <v>871766</v>
       </c>
       <c r="R36" t="n">
-        <v>7441501</v>
+        <v>7441445</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4313,11 +4318,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4344,10 +4344,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117972971</v>
+        <v>117972975</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,42 +4356,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>871841</v>
+        <v>871806</v>
       </c>
       <c r="R37" t="n">
-        <v>7441558</v>
+        <v>7441478</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4426,18 +4422,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4456,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117972954</v>
+        <v>117972971</v>
       </c>
       <c r="B38" t="n">
-        <v>97857</v>
+        <v>97836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4468,38 +4458,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>871817</v>
+        <v>871841</v>
       </c>
       <c r="R38" t="n">
-        <v>7441499</v>
+        <v>7441558</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4534,12 +4528,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117972957</v>
+        <v>117972954</v>
       </c>
       <c r="B39" t="n">
-        <v>96797</v>
+        <v>97857</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4574,21 +4574,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>871810</v>
+        <v>871817</v>
       </c>
       <c r="R39" t="n">
-        <v>7441526</v>
+        <v>7441499</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117985315</v>
+        <v>117985307</v>
       </c>
       <c r="B40" t="n">
         <v>78480</v>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>871662</v>
+        <v>871946</v>
       </c>
       <c r="R40" t="n">
-        <v>7441499</v>
+        <v>7441550</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117985307</v>
+        <v>117985318</v>
       </c>
       <c r="B41" t="n">
         <v>78480</v>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>871946</v>
+        <v>871601</v>
       </c>
       <c r="R41" t="n">
-        <v>7441550</v>
+        <v>7441520</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117985302</v>
+        <v>117985312</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4876,25 +4876,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>871733</v>
+        <v>871779</v>
       </c>
       <c r="R42" t="n">
-        <v>7441449</v>
+        <v>7441554</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117985314</v>
+        <v>117985326</v>
       </c>
       <c r="B43" t="n">
         <v>78480</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>871683</v>
+        <v>871920</v>
       </c>
       <c r="R43" t="n">
-        <v>7441486</v>
+        <v>7441524</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117985321</v>
+        <v>117985302</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,25 +5080,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>871819</v>
+        <v>871733</v>
       </c>
       <c r="R44" t="n">
-        <v>7441537</v>
+        <v>7441449</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117985318</v>
+        <v>117985316</v>
       </c>
       <c r="B45" t="n">
         <v>78480</v>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>871601</v>
+        <v>871638</v>
       </c>
       <c r="R45" t="n">
-        <v>7441520</v>
+        <v>7441502</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5272,7 +5272,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117985310</v>
+        <v>117985311</v>
       </c>
       <c r="B46" t="n">
         <v>78480</v>
@@ -5312,10 +5312,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>871810</v>
+        <v>871826</v>
       </c>
       <c r="R46" t="n">
-        <v>7441482</v>
+        <v>7441578</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5374,10 +5374,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117985303</v>
+        <v>117985309</v>
       </c>
       <c r="B47" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5386,25 +5386,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>871894</v>
+        <v>871943</v>
       </c>
       <c r="R47" t="n">
-        <v>7441401</v>
+        <v>7441513</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5458,7 +5458,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5477,10 +5476,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117985298</v>
+        <v>117985321</v>
       </c>
       <c r="B48" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,21 +5492,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5517,10 +5516,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>871827</v>
+        <v>871819</v>
       </c>
       <c r="R48" t="n">
-        <v>7441544</v>
+        <v>7441537</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5579,7 +5578,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117985326</v>
+        <v>117985319</v>
       </c>
       <c r="B49" t="n">
         <v>78480</v>
@@ -5619,10 +5618,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>871920</v>
+        <v>871677</v>
       </c>
       <c r="R49" t="n">
-        <v>7441524</v>
+        <v>7441539</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5681,10 +5680,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117985311</v>
+        <v>117985299</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5697,21 +5696,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5721,10 +5720,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>871826</v>
+        <v>871660</v>
       </c>
       <c r="R50" t="n">
-        <v>7441578</v>
+        <v>7441500</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5757,6 +5756,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5783,7 +5787,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117985325</v>
+        <v>117985310</v>
       </c>
       <c r="B51" t="n">
         <v>78480</v>
@@ -5823,10 +5827,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>871934</v>
+        <v>871810</v>
       </c>
       <c r="R51" t="n">
-        <v>7441488</v>
+        <v>7441482</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -5885,7 +5889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117985324</v>
+        <v>117985323</v>
       </c>
       <c r="B52" t="n">
         <v>78480</v>
@@ -5925,10 +5929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>871792</v>
+        <v>871789</v>
       </c>
       <c r="R52" t="n">
-        <v>7441439</v>
+        <v>7441477</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -5987,10 +5991,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117985319</v>
+        <v>117985305</v>
       </c>
       <c r="B53" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5999,25 +6003,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6027,10 +6031,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>871677</v>
+        <v>871855</v>
       </c>
       <c r="R53" t="n">
-        <v>7441539</v>
+        <v>7441426</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6196,10 +6200,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117985305</v>
+        <v>117985315</v>
       </c>
       <c r="B55" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6208,25 +6212,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6236,10 +6240,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>871855</v>
+        <v>871662</v>
       </c>
       <c r="R55" t="n">
-        <v>7441426</v>
+        <v>7441499</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6298,7 +6302,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117985327</v>
+        <v>117985324</v>
       </c>
       <c r="B56" t="n">
         <v>78480</v>
@@ -6338,10 +6342,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>871916</v>
+        <v>871792</v>
       </c>
       <c r="R56" t="n">
-        <v>7441528</v>
+        <v>7441439</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6400,7 +6404,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117985323</v>
+        <v>117985320</v>
       </c>
       <c r="B57" t="n">
         <v>78480</v>
@@ -6440,10 +6444,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>871789</v>
+        <v>871762</v>
       </c>
       <c r="R57" t="n">
-        <v>7441477</v>
+        <v>7441517</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6502,10 +6506,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117985301</v>
+        <v>117985325</v>
       </c>
       <c r="B58" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6518,21 +6522,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6542,10 +6546,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>871769</v>
+        <v>871934</v>
       </c>
       <c r="R58" t="n">
-        <v>7441504</v>
+        <v>7441488</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6578,11 +6582,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6609,10 +6608,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117985316</v>
+        <v>117985301</v>
       </c>
       <c r="B59" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6625,21 +6624,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6649,10 +6648,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>871638</v>
+        <v>871769</v>
       </c>
       <c r="R59" t="n">
-        <v>7441502</v>
+        <v>7441504</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6685,6 +6684,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6711,7 +6715,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117985312</v>
+        <v>117985314</v>
       </c>
       <c r="B60" t="n">
         <v>78480</v>
@@ -6751,10 +6755,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>871779</v>
+        <v>871683</v>
       </c>
       <c r="R60" t="n">
-        <v>7441554</v>
+        <v>7441486</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6813,7 +6817,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117985309</v>
+        <v>117985313</v>
       </c>
       <c r="B61" t="n">
         <v>78480</v>
@@ -6853,10 +6857,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>871943</v>
+        <v>871781</v>
       </c>
       <c r="R61" t="n">
-        <v>7441513</v>
+        <v>7441465</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -6915,10 +6919,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117985299</v>
+        <v>117985327</v>
       </c>
       <c r="B62" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6931,21 +6935,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6955,10 +6959,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>871660</v>
+        <v>871916</v>
       </c>
       <c r="R62" t="n">
-        <v>7441500</v>
+        <v>7441528</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -6991,11 +6995,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7022,10 +7021,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117985313</v>
+        <v>117985298</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7038,21 +7037,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7062,10 +7061,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>871781</v>
+        <v>871827</v>
       </c>
       <c r="R63" t="n">
-        <v>7441465</v>
+        <v>7441544</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7124,10 +7123,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117985320</v>
+        <v>117985303</v>
       </c>
       <c r="B64" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7136,25 +7135,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7164,10 +7163,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>871762</v>
+        <v>871894</v>
       </c>
       <c r="R64" t="n">
-        <v>7441517</v>
+        <v>7441401</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7208,6 +7207,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117972986</v>
+        <v>117972973</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871918</v>
+        <v>871659</v>
       </c>
       <c r="R2" t="n">
-        <v>7441530</v>
+        <v>7441583</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,12 +757,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117972983</v>
+        <v>117972969</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871793</v>
+        <v>871848</v>
       </c>
       <c r="R3" t="n">
-        <v>7441442</v>
+        <v>7441438</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,12 +869,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117972959</v>
+        <v>117972975</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>871896</v>
+        <v>871806</v>
       </c>
       <c r="R4" t="n">
-        <v>7441398</v>
+        <v>7441478</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,11 +975,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117972961</v>
+        <v>117972981</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>871700</v>
+        <v>871821</v>
       </c>
       <c r="R5" t="n">
-        <v>7441551</v>
+        <v>7441539</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1106,7 @@
         <v>117972948</v>
       </c>
       <c r="B6" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117972973</v>
+        <v>117972980</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,42 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871659</v>
+        <v>871849</v>
       </c>
       <c r="R7" t="n">
-        <v>7441583</v>
+        <v>7441497</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1282,18 +1288,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117972956</v>
+        <v>117972963</v>
       </c>
       <c r="B8" t="n">
-        <v>96797</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871802</v>
+        <v>871771</v>
       </c>
       <c r="R8" t="n">
-        <v>7441495</v>
+        <v>7441497</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1388,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117972981</v>
+        <v>117972983</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>871821</v>
+        <v>871793</v>
       </c>
       <c r="R9" t="n">
-        <v>7441539</v>
+        <v>7441442</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117972977</v>
+        <v>117972951</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>90512</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871676</v>
+        <v>871766</v>
       </c>
       <c r="R10" t="n">
-        <v>7441585</v>
+        <v>7441445</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117972985</v>
+        <v>117972968</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1635,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>871922</v>
+        <v>871809</v>
       </c>
       <c r="R11" t="n">
-        <v>7441513</v>
+        <v>7441501</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1694,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117972946</v>
+        <v>117972982</v>
       </c>
       <c r="B12" t="n">
-        <v>90660</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>871898</v>
+        <v>871783</v>
       </c>
       <c r="R12" t="n">
-        <v>7441555</v>
+        <v>7441488</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1822,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117972968</v>
+        <v>117972957</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>96799</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>871809</v>
+        <v>871810</v>
       </c>
       <c r="R13" t="n">
-        <v>7441501</v>
+        <v>7441526</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1898,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117972958</v>
+        <v>117972959</v>
       </c>
       <c r="B14" t="n">
-        <v>96797</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,25 +1946,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>871865</v>
+        <v>871896</v>
       </c>
       <c r="R14" t="n">
-        <v>7441441</v>
+        <v>7441398</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2005,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117972974</v>
+        <v>117972971</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,38 +2053,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>871944</v>
+        <v>871841</v>
       </c>
       <c r="R15" t="n">
-        <v>7441550</v>
+        <v>7441558</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,12 +2123,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2133,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117972980</v>
+        <v>117972974</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>871849</v>
+        <v>871944</v>
       </c>
       <c r="R16" t="n">
-        <v>7441497</v>
+        <v>7441550</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2235,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117972962</v>
+        <v>117972964</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>871677</v>
+        <v>871821</v>
       </c>
       <c r="R17" t="n">
-        <v>7441598</v>
+        <v>7441503</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4 kvm</t>
+          <t>25 kvm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117972965</v>
+        <v>117972946</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>90662</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,25 +2374,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>871700</v>
+        <v>871898</v>
       </c>
       <c r="R18" t="n">
-        <v>7441545</v>
+        <v>7441555</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2418,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117972979</v>
+        <v>117972961</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,25 +2476,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>871758</v>
+        <v>871700</v>
       </c>
       <c r="R19" t="n">
-        <v>7441521</v>
+        <v>7441551</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2525,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117972984</v>
+        <v>117972985</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2591,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>871806</v>
+        <v>871922</v>
       </c>
       <c r="R20" t="n">
-        <v>7441439</v>
+        <v>7441513</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2653,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117972952</v>
+        <v>117972984</v>
       </c>
       <c r="B21" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>871898</v>
+        <v>871806</v>
       </c>
       <c r="R21" t="n">
-        <v>7441404</v>
+        <v>7441439</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2755,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117972949</v>
+        <v>117972979</v>
       </c>
       <c r="B22" t="n">
-        <v>56499</v>
+        <v>78482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,42 +2787,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>871818</v>
+        <v>871758</v>
       </c>
       <c r="R22" t="n">
-        <v>7441470</v>
+        <v>7441521</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2835,11 +2851,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2866,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117972966</v>
+        <v>117972978</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,25 +2889,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2906,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>871759</v>
+        <v>871672</v>
       </c>
       <c r="R23" t="n">
-        <v>7441511</v>
+        <v>7441536</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2942,11 +2953,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2973,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117972963</v>
+        <v>117972958</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>96799</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>871771</v>
+        <v>871865</v>
       </c>
       <c r="R24" t="n">
-        <v>7441497</v>
+        <v>7441441</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3049,11 +3055,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117972947</v>
+        <v>117972960</v>
       </c>
       <c r="B25" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3092,25 +3093,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3120,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>871772</v>
+        <v>871899</v>
       </c>
       <c r="R25" t="n">
-        <v>7441436</v>
+        <v>7441403</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3156,6 +3157,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3182,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117972953</v>
+        <v>117972949</v>
       </c>
       <c r="B26" t="n">
-        <v>97857</v>
+        <v>56500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3198,34 +3204,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>871812</v>
+        <v>871818</v>
       </c>
       <c r="R26" t="n">
-        <v>7441500</v>
+        <v>7441470</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3258,6 +3268,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,10 +3299,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117972976</v>
+        <v>117972972</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,38 +3311,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>871824</v>
+        <v>871756</v>
       </c>
       <c r="R27" t="n">
-        <v>7441576</v>
+        <v>7441555</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3362,12 +3381,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3386,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117972964</v>
+        <v>117972966</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3426,10 +3451,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>871821</v>
+        <v>871759</v>
       </c>
       <c r="R28" t="n">
-        <v>7441503</v>
+        <v>7441511</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3466,7 +3491,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>25 kvm</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3493,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117972969</v>
+        <v>117972986</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3505,42 +3530,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>871848</v>
+        <v>871918</v>
       </c>
       <c r="R29" t="n">
-        <v>7441438</v>
+        <v>7441530</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3575,18 +3596,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3605,10 +3620,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117972957</v>
+        <v>117972977</v>
       </c>
       <c r="B30" t="n">
-        <v>96797</v>
+        <v>78482</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3617,25 +3632,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3660,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>871810</v>
+        <v>871676</v>
       </c>
       <c r="R30" t="n">
-        <v>7441526</v>
+        <v>7441585</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3707,10 +3722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117972970</v>
+        <v>117972956</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>96799</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3719,42 +3734,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>871719</v>
+        <v>871802</v>
       </c>
       <c r="R31" t="n">
-        <v>7441553</v>
+        <v>7441495</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3789,18 +3800,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3819,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117972960</v>
+        <v>117972947</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
+        <v>90501</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,25 +3836,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3859,10 +3864,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>871899</v>
+        <v>871772</v>
       </c>
       <c r="R32" t="n">
-        <v>7441403</v>
+        <v>7441436</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3895,11 +3900,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3926,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117972972</v>
+        <v>117972954</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>97859</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,42 +3938,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>871756</v>
+        <v>871817</v>
       </c>
       <c r="R33" t="n">
-        <v>7441555</v>
+        <v>7441499</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4008,18 +4004,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4038,10 +4028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117972982</v>
+        <v>117972970</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4050,38 +4040,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>871783</v>
+        <v>871719</v>
       </c>
       <c r="R34" t="n">
-        <v>7441488</v>
+        <v>7441553</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4116,12 +4110,18 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117972978</v>
+        <v>117972962</v>
       </c>
       <c r="B35" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4152,25 +4152,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>871672</v>
+        <v>871677</v>
       </c>
       <c r="R35" t="n">
-        <v>7441536</v>
+        <v>7441598</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4216,6 +4216,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4242,10 +4247,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117972951</v>
+        <v>117972976</v>
       </c>
       <c r="B36" t="n">
-        <v>90510</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,25 +4259,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4282,10 +4287,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>871766</v>
+        <v>871824</v>
       </c>
       <c r="R36" t="n">
-        <v>7441445</v>
+        <v>7441576</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4344,10 +4349,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117972975</v>
+        <v>117972953</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,25 +4361,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4384,10 +4389,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>871806</v>
+        <v>871812</v>
       </c>
       <c r="R37" t="n">
-        <v>7441478</v>
+        <v>7441500</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4446,10 +4451,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117972971</v>
+        <v>117972952</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>97859</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4458,42 +4463,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>871841</v>
+        <v>871898</v>
       </c>
       <c r="R38" t="n">
-        <v>7441558</v>
+        <v>7441404</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4528,18 +4529,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4553,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117972954</v>
+        <v>117972965</v>
       </c>
       <c r="B39" t="n">
-        <v>97857</v>
+        <v>97838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,25 +4565,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4598,10 +4593,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>871817</v>
+        <v>871700</v>
       </c>
       <c r="R39" t="n">
-        <v>7441499</v>
+        <v>7441545</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4634,6 +4629,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4660,10 +4660,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117985307</v>
+        <v>117985312</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>871946</v>
+        <v>871779</v>
       </c>
       <c r="R40" t="n">
-        <v>7441550</v>
+        <v>7441554</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117985318</v>
+        <v>117985320</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>871601</v>
+        <v>871762</v>
       </c>
       <c r="R41" t="n">
-        <v>7441520</v>
+        <v>7441517</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117985312</v>
+        <v>117985323</v>
       </c>
       <c r="B42" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>871779</v>
+        <v>871789</v>
       </c>
       <c r="R42" t="n">
-        <v>7441554</v>
+        <v>7441477</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4969,7 +4969,7 @@
         <v>117985326</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117985302</v>
+        <v>117985313</v>
       </c>
       <c r="B44" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,25 +5080,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>871733</v>
+        <v>871781</v>
       </c>
       <c r="R44" t="n">
-        <v>7441449</v>
+        <v>7441465</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5170,10 +5170,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117985316</v>
+        <v>117985307</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>871638</v>
+        <v>871946</v>
       </c>
       <c r="R45" t="n">
-        <v>7441502</v>
+        <v>7441550</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5272,10 +5272,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117985311</v>
+        <v>117985300</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5288,21 +5288,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5312,10 +5312,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>871826</v>
+        <v>871739</v>
       </c>
       <c r="R46" t="n">
-        <v>7441578</v>
+        <v>7441532</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5348,6 +5348,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5374,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117985309</v>
+        <v>117985299</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5390,21 +5395,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>871943</v>
+        <v>871660</v>
       </c>
       <c r="R47" t="n">
-        <v>7441513</v>
+        <v>7441500</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5450,6 +5455,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5476,10 +5486,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117985321</v>
+        <v>117985301</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5492,21 +5502,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5516,10 +5526,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>871819</v>
+        <v>871769</v>
       </c>
       <c r="R48" t="n">
-        <v>7441537</v>
+        <v>7441504</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5552,6 +5562,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5578,10 +5593,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117985319</v>
+        <v>117985309</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5618,10 +5633,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>871677</v>
+        <v>871943</v>
       </c>
       <c r="R49" t="n">
-        <v>7441539</v>
+        <v>7441513</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5680,10 +5695,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117985299</v>
+        <v>117985302</v>
       </c>
       <c r="B50" t="n">
-        <v>57287</v>
+        <v>79592</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5692,25 +5707,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5720,10 +5735,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>871660</v>
+        <v>871733</v>
       </c>
       <c r="R50" t="n">
-        <v>7441500</v>
+        <v>7441449</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5756,11 +5771,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5787,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117985310</v>
+        <v>117985316</v>
       </c>
       <c r="B51" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5827,10 +5837,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>871810</v>
+        <v>871638</v>
       </c>
       <c r="R51" t="n">
-        <v>7441482</v>
+        <v>7441502</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -5889,10 +5899,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117985323</v>
+        <v>117985319</v>
       </c>
       <c r="B52" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5929,10 +5939,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>871789</v>
+        <v>871677</v>
       </c>
       <c r="R52" t="n">
-        <v>7441477</v>
+        <v>7441539</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -5991,10 +6001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117985305</v>
+        <v>117985311</v>
       </c>
       <c r="B53" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6003,25 +6013,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6031,10 +6041,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>871855</v>
+        <v>871826</v>
       </c>
       <c r="R53" t="n">
-        <v>7441426</v>
+        <v>7441578</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6093,10 +6103,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117985300</v>
+        <v>117985321</v>
       </c>
       <c r="B54" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6109,21 +6119,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6133,10 +6143,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>871739</v>
+        <v>871819</v>
       </c>
       <c r="R54" t="n">
-        <v>7441532</v>
+        <v>7441537</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6169,11 +6179,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6200,10 +6205,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117985315</v>
+        <v>117985310</v>
       </c>
       <c r="B55" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>871662</v>
+        <v>871810</v>
       </c>
       <c r="R55" t="n">
-        <v>7441499</v>
+        <v>7441482</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6305,7 +6310,7 @@
         <v>117985324</v>
       </c>
       <c r="B56" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6404,10 +6409,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117985320</v>
+        <v>117985327</v>
       </c>
       <c r="B57" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6444,10 +6449,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>871762</v>
+        <v>871916</v>
       </c>
       <c r="R57" t="n">
-        <v>7441517</v>
+        <v>7441528</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6506,10 +6511,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117985325</v>
+        <v>117985315</v>
       </c>
       <c r="B58" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6546,10 +6551,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>871934</v>
+        <v>871662</v>
       </c>
       <c r="R58" t="n">
-        <v>7441488</v>
+        <v>7441499</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6608,10 +6613,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117985301</v>
+        <v>117985318</v>
       </c>
       <c r="B59" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6624,21 +6629,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6648,10 +6653,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>871769</v>
+        <v>871601</v>
       </c>
       <c r="R59" t="n">
-        <v>7441504</v>
+        <v>7441520</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6684,11 +6689,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6715,10 +6715,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117985314</v>
+        <v>117985325</v>
       </c>
       <c r="B60" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>871683</v>
+        <v>871934</v>
       </c>
       <c r="R60" t="n">
-        <v>7441486</v>
+        <v>7441488</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117985313</v>
+        <v>117985303</v>
       </c>
       <c r="B61" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6829,25 +6829,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>871781</v>
+        <v>871894</v>
       </c>
       <c r="R61" t="n">
-        <v>7441465</v>
+        <v>7441401</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -6901,6 +6901,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6919,10 +6920,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117985327</v>
+        <v>117985314</v>
       </c>
       <c r="B62" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6959,10 +6960,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>871916</v>
+        <v>871683</v>
       </c>
       <c r="R62" t="n">
-        <v>7441528</v>
+        <v>7441486</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7021,10 +7022,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117985298</v>
+        <v>117985305</v>
       </c>
       <c r="B63" t="n">
-        <v>90517</v>
+        <v>97859</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7033,25 +7034,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7061,10 +7062,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>871827</v>
+        <v>871855</v>
       </c>
       <c r="R63" t="n">
-        <v>7441544</v>
+        <v>7441426</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7123,10 +7124,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117985303</v>
+        <v>117985298</v>
       </c>
       <c r="B64" t="n">
-        <v>97857</v>
+        <v>90519</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7135,25 +7136,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7163,10 +7164,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>871894</v>
+        <v>871827</v>
       </c>
       <c r="R64" t="n">
-        <v>7441401</v>
+        <v>7441544</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7207,7 +7208,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>118020738</v>
       </c>
       <c r="B65" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117972951</v>
+        <v>117972968</v>
       </c>
       <c r="B10" t="n">
-        <v>90512</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871766</v>
+        <v>871809</v>
       </c>
       <c r="R10" t="n">
-        <v>7441445</v>
+        <v>7441501</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1597,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117972968</v>
+        <v>117972951</v>
       </c>
       <c r="B11" t="n">
-        <v>97838</v>
+        <v>90512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,25 +1640,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>871809</v>
+        <v>871766</v>
       </c>
       <c r="R11" t="n">
-        <v>7441501</v>
+        <v>7441445</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117972957</v>
+        <v>117972959</v>
       </c>
       <c r="B13" t="n">
-        <v>96799</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>871810</v>
+        <v>871896</v>
       </c>
       <c r="R13" t="n">
-        <v>7441526</v>
+        <v>7441398</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1908,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117972959</v>
+        <v>117972971</v>
       </c>
       <c r="B14" t="n">
         <v>97838</v>
@@ -1968,16 +1973,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>871896</v>
+        <v>871841</v>
       </c>
       <c r="R14" t="n">
-        <v>7441398</v>
+        <v>7441558</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,6 +2032,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2041,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117972971</v>
+        <v>117972957</v>
       </c>
       <c r="B15" t="n">
-        <v>97838</v>
+        <v>96799</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,42 +2063,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>871841</v>
+        <v>871810</v>
       </c>
       <c r="R15" t="n">
-        <v>7441558</v>
+        <v>7441526</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2123,18 +2129,12 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117972961</v>
+        <v>117972985</v>
       </c>
       <c r="B19" t="n">
-        <v>97838</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,25 +2476,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>871700</v>
+        <v>871922</v>
       </c>
       <c r="R19" t="n">
-        <v>7441551</v>
+        <v>7441513</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2540,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117972985</v>
+        <v>117972984</v>
       </c>
       <c r="B20" t="n">
         <v>78482</v>
@@ -2611,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>871922</v>
+        <v>871806</v>
       </c>
       <c r="R20" t="n">
-        <v>7441513</v>
+        <v>7441439</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2673,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117972984</v>
+        <v>117972961</v>
       </c>
       <c r="B21" t="n">
-        <v>78482</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2680,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>871806</v>
+        <v>871700</v>
       </c>
       <c r="R21" t="n">
-        <v>7441439</v>
+        <v>7441551</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2749,6 +2744,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4 kvm</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7965,10 +7965,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118442117</v>
+        <v>118442122</v>
       </c>
       <c r="B72" t="n">
-        <v>57290</v>
+        <v>96801</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7977,25 +7977,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>872049</v>
+        <v>872099</v>
       </c>
       <c r="R72" t="n">
-        <v>7441494</v>
+        <v>7441526</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8041,11 +8041,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8072,10 +8067,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118442122</v>
+        <v>118444235</v>
       </c>
       <c r="B73" t="n">
-        <v>96801</v>
+        <v>96807</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8088,16 +8083,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8108,14 +8103,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>872099</v>
+        <v>872313</v>
       </c>
       <c r="R73" t="n">
-        <v>7441526</v>
+        <v>7441655</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8162,22 +8157,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118444235</v>
+        <v>118442117</v>
       </c>
       <c r="B74" t="n">
-        <v>96807</v>
+        <v>57290</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8186,38 +8181,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>872313</v>
+        <v>872049</v>
       </c>
       <c r="R74" t="n">
-        <v>7441655</v>
+        <v>7441494</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8252,6 +8247,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8264,12 +8264,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7965,10 +7965,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118442122</v>
+        <v>118442117</v>
       </c>
       <c r="B72" t="n">
-        <v>96801</v>
+        <v>57290</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7977,25 +7977,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>872099</v>
+        <v>872049</v>
       </c>
       <c r="R72" t="n">
-        <v>7441526</v>
+        <v>7441494</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8041,6 +8041,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8067,10 +8072,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118444235</v>
+        <v>118442122</v>
       </c>
       <c r="B73" t="n">
-        <v>96807</v>
+        <v>96801</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8083,16 +8088,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8103,14 +8108,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>872313</v>
+        <v>872099</v>
       </c>
       <c r="R73" t="n">
-        <v>7441655</v>
+        <v>7441526</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8157,22 +8162,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118442117</v>
+        <v>118444235</v>
       </c>
       <c r="B74" t="n">
-        <v>57290</v>
+        <v>96807</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8181,38 +8186,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>872049</v>
+        <v>872313</v>
       </c>
       <c r="R74" t="n">
-        <v>7441494</v>
+        <v>7441655</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8247,11 +8252,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8264,22 +8264,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118442119</v>
+        <v>118442126</v>
       </c>
       <c r="B75" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8292,21 +8292,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
         <v>872014</v>
       </c>
       <c r="R75" t="n">
-        <v>7441505</v>
+        <v>7441531</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8352,11 +8352,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8383,10 +8378,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118442126</v>
+        <v>118442119</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8426,7 +8421,7 @@
         <v>872014</v>
       </c>
       <c r="R76" t="n">
-        <v>7441531</v>
+        <v>7441505</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8459,6 +8454,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7455,10 +7455,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118442124</v>
+        <v>118442123</v>
       </c>
       <c r="B67" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7467,25 +7467,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>872014</v>
+        <v>872048</v>
       </c>
       <c r="R67" t="n">
-        <v>7441493</v>
+        <v>7441509</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7557,10 +7557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118442121</v>
+        <v>118444234</v>
       </c>
       <c r="B68" t="n">
-        <v>96801</v>
+        <v>96807</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7573,16 +7573,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7593,14 +7593,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>872171</v>
+        <v>872383</v>
       </c>
       <c r="R68" t="n">
-        <v>7441451</v>
+        <v>7441674</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7647,22 +7647,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118446301</v>
+        <v>118442125</v>
       </c>
       <c r="B69" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7671,25 +7671,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>872091</v>
+        <v>872011</v>
       </c>
       <c r="R69" t="n">
-        <v>7441501</v>
+        <v>7441512</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7749,12 +7749,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118442125</v>
+        <v>118442122</v>
       </c>
       <c r="B71" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7875,25 +7875,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7903,10 +7903,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>872011</v>
+        <v>872099</v>
       </c>
       <c r="R71" t="n">
-        <v>7441512</v>
+        <v>7441526</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118442117</v>
+        <v>118442119</v>
       </c>
       <c r="B72" t="n">
         <v>57290</v>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>872049</v>
+        <v>872014</v>
       </c>
       <c r="R72" t="n">
-        <v>7441494</v>
+        <v>7441505</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118442122</v>
+        <v>118442124</v>
       </c>
       <c r="B73" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8084,25 +8084,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>872099</v>
+        <v>872014</v>
       </c>
       <c r="R73" t="n">
-        <v>7441526</v>
+        <v>7441493</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8174,10 +8174,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118444235</v>
+        <v>118444230</v>
       </c>
       <c r="B74" t="n">
-        <v>96807</v>
+        <v>57290</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8186,25 +8186,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>872313</v>
+        <v>872270</v>
       </c>
       <c r="R74" t="n">
-        <v>7441655</v>
+        <v>7441625</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118442126</v>
+        <v>118446304</v>
       </c>
       <c r="B75" t="n">
         <v>78484</v>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>872014</v>
+        <v>872018</v>
       </c>
       <c r="R75" t="n">
-        <v>7441531</v>
+        <v>7441540</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8366,22 +8366,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118442119</v>
+        <v>118444235</v>
       </c>
       <c r="B76" t="n">
-        <v>57290</v>
+        <v>96807</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8390,38 +8390,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>872014</v>
+        <v>872313</v>
       </c>
       <c r="R76" t="n">
-        <v>7441505</v>
+        <v>7441655</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8456,11 +8456,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8473,22 +8468,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118444230</v>
+        <v>118442120</v>
       </c>
       <c r="B77" t="n">
-        <v>57290</v>
+        <v>97867</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8497,38 +8492,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>872270</v>
+        <v>872035</v>
       </c>
       <c r="R77" t="n">
-        <v>7441625</v>
+        <v>7441431</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8575,22 +8570,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118442123</v>
+        <v>118442126</v>
       </c>
       <c r="B78" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8599,25 +8594,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8627,10 +8622,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>872048</v>
+        <v>872014</v>
       </c>
       <c r="R78" t="n">
-        <v>7441509</v>
+        <v>7441531</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8689,10 +8684,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118442120</v>
+        <v>118442117</v>
       </c>
       <c r="B79" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8701,25 +8696,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8729,10 +8724,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>872035</v>
+        <v>872049</v>
       </c>
       <c r="R79" t="n">
-        <v>7441431</v>
+        <v>7441494</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8765,6 +8760,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8893,10 +8893,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118444234</v>
+        <v>118446301</v>
       </c>
       <c r="B81" t="n">
-        <v>96807</v>
+        <v>96801</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8909,16 +8909,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8929,14 +8929,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>872383</v>
+        <v>872091</v>
       </c>
       <c r="R81" t="n">
-        <v>7441674</v>
+        <v>7441501</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8995,10 +8995,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118446304</v>
+        <v>118442121</v>
       </c>
       <c r="B82" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9007,25 +9007,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>872018</v>
+        <v>872171</v>
       </c>
       <c r="R82" t="n">
-        <v>7441540</v>
+        <v>7441451</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9085,12 +9085,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -8791,10 +8791,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118446302</v>
+        <v>118446301</v>
       </c>
       <c r="B80" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8803,25 +8803,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>872029</v>
+        <v>872091</v>
       </c>
       <c r="R80" t="n">
-        <v>7441464</v>
+        <v>7441501</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118446301</v>
+        <v>118446302</v>
       </c>
       <c r="B81" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8905,25 +8905,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>872091</v>
+        <v>872029</v>
       </c>
       <c r="R81" t="n">
-        <v>7441501</v>
+        <v>7441464</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7455,7 +7455,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118442123</v>
+        <v>118442121</v>
       </c>
       <c r="B67" t="n">
         <v>96801</v>
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>872048</v>
+        <v>872171</v>
       </c>
       <c r="R67" t="n">
-        <v>7441509</v>
+        <v>7441451</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7557,10 +7557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118444234</v>
+        <v>118442127</v>
       </c>
       <c r="B68" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7569,38 +7569,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>872383</v>
+        <v>872019</v>
       </c>
       <c r="R68" t="n">
-        <v>7441674</v>
+        <v>7441538</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7647,22 +7647,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118442125</v>
+        <v>118446301</v>
       </c>
       <c r="B69" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7671,25 +7671,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>872011</v>
+        <v>872091</v>
       </c>
       <c r="R69" t="n">
-        <v>7441512</v>
+        <v>7441501</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7749,22 +7749,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118442127</v>
+        <v>118442120</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7773,25 +7773,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>872019</v>
+        <v>872035</v>
       </c>
       <c r="R70" t="n">
-        <v>7441538</v>
+        <v>7441431</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -7863,10 +7863,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118442122</v>
+        <v>118444230</v>
       </c>
       <c r="B71" t="n">
-        <v>96801</v>
+        <v>57290</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7875,38 +7875,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>872099</v>
+        <v>872270</v>
       </c>
       <c r="R71" t="n">
-        <v>7441526</v>
+        <v>7441625</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7953,22 +7953,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118442119</v>
+        <v>118442122</v>
       </c>
       <c r="B72" t="n">
-        <v>57290</v>
+        <v>96801</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7977,25 +7977,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>872014</v>
+        <v>872099</v>
       </c>
       <c r="R72" t="n">
-        <v>7441505</v>
+        <v>7441526</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8041,11 +8041,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8072,10 +8067,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118442124</v>
+        <v>118444235</v>
       </c>
       <c r="B73" t="n">
-        <v>78484</v>
+        <v>96807</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8084,38 +8079,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>872014</v>
+        <v>872313</v>
       </c>
       <c r="R73" t="n">
-        <v>7441493</v>
+        <v>7441655</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8162,22 +8157,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118444230</v>
+        <v>118442123</v>
       </c>
       <c r="B74" t="n">
-        <v>57290</v>
+        <v>96801</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8186,38 +8181,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>872270</v>
+        <v>872048</v>
       </c>
       <c r="R74" t="n">
-        <v>7441625</v>
+        <v>7441509</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8264,22 +8259,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118446304</v>
+        <v>118442119</v>
       </c>
       <c r="B75" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8292,21 +8287,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8316,10 +8311,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>872018</v>
+        <v>872014</v>
       </c>
       <c r="R75" t="n">
-        <v>7441540</v>
+        <v>7441505</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8354,6 +8349,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8366,22 +8366,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118444235</v>
+        <v>118446302</v>
       </c>
       <c r="B76" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8390,38 +8390,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>872313</v>
+        <v>872029</v>
       </c>
       <c r="R76" t="n">
-        <v>7441655</v>
+        <v>7441464</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118442120</v>
+        <v>118442126</v>
       </c>
       <c r="B77" t="n">
-        <v>97867</v>
+        <v>78484</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8492,25 +8492,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>872035</v>
+        <v>872014</v>
       </c>
       <c r="R77" t="n">
-        <v>7441431</v>
+        <v>7441531</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118442126</v>
+        <v>118446304</v>
       </c>
       <c r="B78" t="n">
         <v>78484</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>872014</v>
+        <v>872018</v>
       </c>
       <c r="R78" t="n">
-        <v>7441531</v>
+        <v>7441540</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8672,22 +8672,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118442117</v>
+        <v>118444234</v>
       </c>
       <c r="B79" t="n">
-        <v>57290</v>
+        <v>96807</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8696,38 +8696,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>872049</v>
+        <v>872383</v>
       </c>
       <c r="R79" t="n">
-        <v>7441494</v>
+        <v>7441674</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8762,11 +8762,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8779,22 +8774,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118446301</v>
+        <v>118442117</v>
       </c>
       <c r="B80" t="n">
-        <v>96801</v>
+        <v>57290</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8803,25 +8798,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8831,10 +8826,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>872091</v>
+        <v>872049</v>
       </c>
       <c r="R80" t="n">
-        <v>7441501</v>
+        <v>7441494</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8869,6 +8864,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8881,19 +8881,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118446302</v>
+        <v>118442124</v>
       </c>
       <c r="B81" t="n">
         <v>78484</v>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>872029</v>
+        <v>872014</v>
       </c>
       <c r="R81" t="n">
-        <v>7441464</v>
+        <v>7441493</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8983,22 +8983,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118442121</v>
+        <v>118442125</v>
       </c>
       <c r="B82" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9007,25 +9007,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>872171</v>
+        <v>872011</v>
       </c>
       <c r="R82" t="n">
-        <v>7441451</v>
+        <v>7441512</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7455,10 +7455,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118442121</v>
+        <v>118442119</v>
       </c>
       <c r="B67" t="n">
-        <v>96801</v>
+        <v>57290</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7467,25 +7467,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>872171</v>
+        <v>872014</v>
       </c>
       <c r="R67" t="n">
-        <v>7441451</v>
+        <v>7441505</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7531,6 +7531,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7557,10 +7562,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118442127</v>
+        <v>118444234</v>
       </c>
       <c r="B68" t="n">
-        <v>78484</v>
+        <v>96814</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7569,38 +7574,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>872019</v>
+        <v>872383</v>
       </c>
       <c r="R68" t="n">
-        <v>7441538</v>
+        <v>7441674</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7647,22 +7652,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118446301</v>
+        <v>118446302</v>
       </c>
       <c r="B69" t="n">
-        <v>96801</v>
+        <v>78491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7671,25 +7676,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7699,10 +7704,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>872091</v>
+        <v>872029</v>
       </c>
       <c r="R69" t="n">
-        <v>7441501</v>
+        <v>7441464</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7761,10 +7766,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118442120</v>
+        <v>118446304</v>
       </c>
       <c r="B70" t="n">
-        <v>97867</v>
+        <v>78491</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7773,25 +7778,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7801,10 +7806,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>872035</v>
+        <v>872018</v>
       </c>
       <c r="R70" t="n">
-        <v>7441431</v>
+        <v>7441540</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -7851,22 +7856,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118444230</v>
+        <v>118442122</v>
       </c>
       <c r="B71" t="n">
-        <v>57290</v>
+        <v>96808</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7875,38 +7880,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>872270</v>
+        <v>872099</v>
       </c>
       <c r="R71" t="n">
-        <v>7441625</v>
+        <v>7441526</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7953,22 +7958,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118442122</v>
+        <v>118442121</v>
       </c>
       <c r="B72" t="n">
-        <v>96801</v>
+        <v>96808</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>872099</v>
+        <v>872171</v>
       </c>
       <c r="R72" t="n">
-        <v>7441526</v>
+        <v>7441451</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8067,10 +8072,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118444235</v>
+        <v>118442126</v>
       </c>
       <c r="B73" t="n">
-        <v>96807</v>
+        <v>78491</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8079,38 +8084,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>872313</v>
+        <v>872014</v>
       </c>
       <c r="R73" t="n">
-        <v>7441655</v>
+        <v>7441531</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8157,22 +8162,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118442123</v>
+        <v>118442125</v>
       </c>
       <c r="B74" t="n">
-        <v>96801</v>
+        <v>78491</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8181,25 +8186,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8209,10 +8214,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>872048</v>
+        <v>872011</v>
       </c>
       <c r="R74" t="n">
-        <v>7441509</v>
+        <v>7441512</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8271,10 +8276,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118442119</v>
+        <v>118442123</v>
       </c>
       <c r="B75" t="n">
-        <v>57290</v>
+        <v>96808</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8283,25 +8288,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8311,10 +8316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>872014</v>
+        <v>872048</v>
       </c>
       <c r="R75" t="n">
-        <v>7441505</v>
+        <v>7441509</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8347,11 +8352,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118446302</v>
+        <v>118444230</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8394,34 +8394,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>872029</v>
+        <v>872270</v>
       </c>
       <c r="R76" t="n">
-        <v>7441464</v>
+        <v>7441625</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118442126</v>
+        <v>118446301</v>
       </c>
       <c r="B77" t="n">
-        <v>78484</v>
+        <v>96808</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8492,25 +8492,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>872014</v>
+        <v>872091</v>
       </c>
       <c r="R77" t="n">
-        <v>7441531</v>
+        <v>7441501</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8570,22 +8570,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118446304</v>
+        <v>118442124</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>872018</v>
+        <v>872014</v>
       </c>
       <c r="R78" t="n">
-        <v>7441540</v>
+        <v>7441493</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8672,22 +8672,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118444234</v>
+        <v>118442117</v>
       </c>
       <c r="B79" t="n">
-        <v>96807</v>
+        <v>57290</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8696,38 +8696,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>872383</v>
+        <v>872049</v>
       </c>
       <c r="R79" t="n">
-        <v>7441674</v>
+        <v>7441494</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8762,6 +8762,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8774,22 +8779,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118442117</v>
+        <v>118442120</v>
       </c>
       <c r="B80" t="n">
-        <v>57290</v>
+        <v>97874</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8798,25 +8803,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8826,10 +8831,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>872049</v>
+        <v>872035</v>
       </c>
       <c r="R80" t="n">
-        <v>7441494</v>
+        <v>7441431</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8862,11 +8867,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8893,10 +8893,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118442124</v>
+        <v>118444235</v>
       </c>
       <c r="B81" t="n">
-        <v>78484</v>
+        <v>96814</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8905,38 +8905,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>872014</v>
+        <v>872313</v>
       </c>
       <c r="R81" t="n">
-        <v>7441493</v>
+        <v>7441655</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8983,22 +8983,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118442125</v>
+        <v>118442127</v>
       </c>
       <c r="B82" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>872011</v>
+        <v>872019</v>
       </c>
       <c r="R82" t="n">
-        <v>7441512</v>
+        <v>7441538</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7562,10 +7562,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118444234</v>
+        <v>118446302</v>
       </c>
       <c r="B68" t="n">
-        <v>96814</v>
+        <v>78491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7574,38 +7574,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>872383</v>
+        <v>872029</v>
       </c>
       <c r="R68" t="n">
-        <v>7441674</v>
+        <v>7441464</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7664,10 +7664,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118446302</v>
+        <v>118444234</v>
       </c>
       <c r="B69" t="n">
-        <v>78491</v>
+        <v>96814</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7676,38 +7676,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>872029</v>
+        <v>872383</v>
       </c>
       <c r="R69" t="n">
-        <v>7441464</v>
+        <v>7441674</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118442124</v>
+        <v>118442120</v>
       </c>
       <c r="B78" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8594,25 +8594,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>872014</v>
+        <v>872035</v>
       </c>
       <c r="R78" t="n">
-        <v>7441493</v>
+        <v>7441431</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8684,10 +8684,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118442117</v>
+        <v>118442124</v>
       </c>
       <c r="B79" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>872049</v>
+        <v>872014</v>
       </c>
       <c r="R79" t="n">
-        <v>7441494</v>
+        <v>7441493</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8760,11 +8760,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8791,10 +8786,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118442120</v>
+        <v>118442117</v>
       </c>
       <c r="B80" t="n">
-        <v>97874</v>
+        <v>57290</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8803,25 +8798,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8831,10 +8826,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>872035</v>
+        <v>872049</v>
       </c>
       <c r="R80" t="n">
-        <v>7441431</v>
+        <v>7441494</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8867,6 +8862,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -7455,7 +7455,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118442119</v>
+        <v>118444230</v>
       </c>
       <c r="B67" t="n">
         <v>57290</v>
@@ -7491,14 +7491,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>872014</v>
+        <v>872270</v>
       </c>
       <c r="R67" t="n">
-        <v>7441505</v>
+        <v>7441625</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7533,11 +7533,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7550,19 +7545,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118446302</v>
+        <v>118442126</v>
       </c>
       <c r="B68" t="n">
         <v>78491</v>
@@ -7602,10 +7597,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>872029</v>
+        <v>872014</v>
       </c>
       <c r="R68" t="n">
-        <v>7441464</v>
+        <v>7441531</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7652,22 +7647,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118444234</v>
+        <v>118442117</v>
       </c>
       <c r="B69" t="n">
-        <v>96814</v>
+        <v>57290</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7676,38 +7671,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>872383</v>
+        <v>872049</v>
       </c>
       <c r="R69" t="n">
-        <v>7441674</v>
+        <v>7441494</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7742,6 +7737,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7754,22 +7754,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118446304</v>
+        <v>118442121</v>
       </c>
       <c r="B70" t="n">
-        <v>78491</v>
+        <v>96808</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7778,25 +7778,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>872018</v>
+        <v>872171</v>
       </c>
       <c r="R70" t="n">
-        <v>7441540</v>
+        <v>7441451</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -7856,22 +7856,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118442122</v>
+        <v>118442127</v>
       </c>
       <c r="B71" t="n">
-        <v>96808</v>
+        <v>78491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7880,25 +7880,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>872099</v>
+        <v>872019</v>
       </c>
       <c r="R71" t="n">
-        <v>7441526</v>
+        <v>7441538</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118442121</v>
+        <v>118442125</v>
       </c>
       <c r="B72" t="n">
-        <v>96808</v>
+        <v>78491</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7982,25 +7982,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>872171</v>
+        <v>872011</v>
       </c>
       <c r="R72" t="n">
-        <v>7441451</v>
+        <v>7441512</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118442126</v>
+        <v>118442123</v>
       </c>
       <c r="B73" t="n">
-        <v>78491</v>
+        <v>96808</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8084,25 +8084,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>872014</v>
+        <v>872048</v>
       </c>
       <c r="R73" t="n">
-        <v>7441531</v>
+        <v>7441509</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8174,10 +8174,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118442125</v>
+        <v>118442120</v>
       </c>
       <c r="B74" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8186,25 +8186,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>872011</v>
+        <v>872035</v>
       </c>
       <c r="R74" t="n">
-        <v>7441512</v>
+        <v>7441431</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118442123</v>
+        <v>118442124</v>
       </c>
       <c r="B75" t="n">
-        <v>96808</v>
+        <v>78491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8288,25 +8288,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>872048</v>
+        <v>872014</v>
       </c>
       <c r="R75" t="n">
-        <v>7441509</v>
+        <v>7441493</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8378,10 +8378,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118444230</v>
+        <v>118446304</v>
       </c>
       <c r="B76" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8394,34 +8394,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>872270</v>
+        <v>872018</v>
       </c>
       <c r="R76" t="n">
-        <v>7441625</v>
+        <v>7441540</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118442120</v>
+        <v>118444235</v>
       </c>
       <c r="B78" t="n">
-        <v>97874</v>
+        <v>96814</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8598,34 +8598,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>872035</v>
+        <v>872313</v>
       </c>
       <c r="R78" t="n">
-        <v>7441431</v>
+        <v>7441655</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8672,22 +8672,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118442124</v>
+        <v>118444234</v>
       </c>
       <c r="B79" t="n">
-        <v>78491</v>
+        <v>96814</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8696,38 +8696,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Koijusaajo, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>872014</v>
+        <v>872383</v>
       </c>
       <c r="R79" t="n">
-        <v>7441493</v>
+        <v>7441674</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8774,22 +8774,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118442117</v>
+        <v>118442122</v>
       </c>
       <c r="B80" t="n">
-        <v>57290</v>
+        <v>96808</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8798,25 +8798,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8826,10 +8826,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>872049</v>
+        <v>872099</v>
       </c>
       <c r="R80" t="n">
-        <v>7441494</v>
+        <v>7441526</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8862,11 +8862,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8893,10 +8888,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118444235</v>
+        <v>118446302</v>
       </c>
       <c r="B81" t="n">
-        <v>96814</v>
+        <v>78491</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8905,38 +8900,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Koijusaajo, Nb</t>
+          <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>872313</v>
+        <v>872029</v>
       </c>
       <c r="R81" t="n">
-        <v>7441655</v>
+        <v>7441464</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8995,10 +8990,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118442127</v>
+        <v>118442119</v>
       </c>
       <c r="B82" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9011,21 +9006,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9035,10 +9030,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>872019</v>
+        <v>872014</v>
       </c>
       <c r="R82" t="n">
-        <v>7441538</v>
+        <v>7441505</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9071,6 +9066,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Avbarkad stam</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -2039,11 +2039,11 @@
         <v>117972948</v>
       </c>
       <c r="B15" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2146,11 +2146,11 @@
         <v>117972949</v>
       </c>
       <c r="B16" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -2039,11 +2039,11 @@
         <v>117972948</v>
       </c>
       <c r="B15" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2146,11 +2146,11 @@
         <v>117972949</v>
       </c>
       <c r="B16" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">

--- a/artfynd/A 22909-2024 artfynd.xlsx
+++ b/artfynd/A 22909-2024 artfynd.xlsx
@@ -9199,32 +9199,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126867202</v>
+        <v>126863352</v>
       </c>
       <c r="B84" t="n">
-        <v>82792</v>
+        <v>91284</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>871946</v>
+        <v>871948</v>
       </c>
       <c r="R84" t="n">
-        <v>7441560</v>
+        <v>7441513</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9281,20 +9281,15 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
-      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9305,10 +9300,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126862991</v>
+        <v>126867202</v>
       </c>
       <c r="B85" t="n">
-        <v>91245</v>
+        <v>82852</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9316,21 +9311,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9340,10 +9335,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>871921</v>
+        <v>871946</v>
       </c>
       <c r="R85" t="n">
-        <v>7441520</v>
+        <v>7441560</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9387,15 +9382,20 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9406,32 +9406,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126863352</v>
+        <v>126862991</v>
       </c>
       <c r="B86" t="n">
-        <v>91210</v>
+        <v>91319</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>871948</v>
+        <v>871921</v>
       </c>
       <c r="R86" t="n">
-        <v>7441513</v>
+        <v>7441520</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9491,12 +9491,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9507,32 +9507,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126863363</v>
+        <v>126863353</v>
       </c>
       <c r="B87" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>871907</v>
+        <v>871847</v>
       </c>
       <c r="R87" t="n">
-        <v>7441522</v>
+        <v>7441524</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9608,32 +9608,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126863353</v>
+        <v>126867218</v>
       </c>
       <c r="B88" t="n">
-        <v>91245</v>
+        <v>79549</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>1353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9643,10 +9643,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>871847</v>
+        <v>871689</v>
       </c>
       <c r="R88" t="n">
-        <v>7441524</v>
+        <v>7441505</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9690,15 +9690,20 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Gammal gran</t>
+        </is>
+      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9709,32 +9714,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126867218</v>
+        <v>126863363</v>
       </c>
       <c r="B89" t="n">
-        <v>79518</v>
+        <v>98436</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1353</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9744,10 +9749,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>871689</v>
+        <v>871907</v>
       </c>
       <c r="R89" t="n">
-        <v>7441505</v>
+        <v>7441522</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9791,20 +9796,15 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Gammal gran</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9815,32 +9815,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126863361</v>
+        <v>126867217</v>
       </c>
       <c r="B90" t="n">
-        <v>98361</v>
+        <v>82852</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9850,10 +9850,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>871708</v>
+        <v>871690</v>
       </c>
       <c r="R90" t="n">
-        <v>7441474</v>
+        <v>7441504</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9897,15 +9897,20 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9916,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126867217</v>
+        <v>126862985</v>
       </c>
       <c r="B91" t="n">
-        <v>82792</v>
+        <v>75135</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9927,21 +9932,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9951,10 +9956,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>871690</v>
+        <v>871974</v>
       </c>
       <c r="R91" t="n">
-        <v>7441504</v>
+        <v>7441472</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9998,20 +10003,15 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
-      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10022,32 +10022,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126862985</v>
+        <v>126863361</v>
       </c>
       <c r="B92" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>871974</v>
+        <v>871708</v>
       </c>
       <c r="R92" t="n">
-        <v>7441472</v>
+        <v>7441474</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10107,12 +10107,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10126,7 +10126,7 @@
         <v>126867219</v>
       </c>
       <c r="B93" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>126867211</v>
       </c>
       <c r="B94" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>126863356</v>
       </c>
       <c r="B95" t="n">
-        <v>79518</v>
+        <v>79549</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>126862989</v>
       </c>
       <c r="B96" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126867205</v>
+        <v>126862988</v>
       </c>
       <c r="B97" t="n">
-        <v>75075</v>
+        <v>91319</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10556,21 +10556,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10580,10 +10580,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>871944</v>
+        <v>871809</v>
       </c>
       <c r="R97" t="n">
-        <v>7441507</v>
+        <v>7441556</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10627,20 +10627,15 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
-      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10651,32 +10646,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126862988</v>
+        <v>126863371</v>
       </c>
       <c r="B98" t="n">
-        <v>91245</v>
+        <v>96562</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10686,10 +10681,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>871809</v>
+        <v>871971</v>
       </c>
       <c r="R98" t="n">
-        <v>7441556</v>
+        <v>7441430</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10736,12 +10731,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10752,32 +10747,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126863371</v>
+        <v>126867205</v>
       </c>
       <c r="B99" t="n">
-        <v>96487</v>
+        <v>75135</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10787,10 +10782,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>871971</v>
+        <v>871944</v>
       </c>
       <c r="R99" t="n">
-        <v>7441430</v>
+        <v>7441507</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10834,15 +10829,20 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10856,7 +10856,7 @@
         <v>126867214</v>
       </c>
       <c r="B100" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>126862987</v>
       </c>
       <c r="B101" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>126863360</v>
       </c>
       <c r="B102" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>126867220</v>
       </c>
       <c r="B103" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>126862996</v>
       </c>
       <c r="B104" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11367,32 +11367,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126863001</v>
+        <v>126863367</v>
       </c>
       <c r="B105" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>871706</v>
+        <v>871939</v>
       </c>
       <c r="R105" t="n">
-        <v>7441475</v>
+        <v>7441558</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,19 +11446,18 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11469,10 +11468,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126867203</v>
+        <v>126863001</v>
       </c>
       <c r="B106" t="n">
-        <v>98382</v>
+        <v>98353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11480,21 +11479,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11504,10 +11503,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>871948</v>
+        <v>871706</v>
       </c>
       <c r="R106" t="n">
-        <v>7441545</v>
+        <v>7441475</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11548,18 +11547,19 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11570,32 +11570,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126863367</v>
+        <v>126867203</v>
       </c>
       <c r="B107" t="n">
-        <v>78980</v>
+        <v>98457</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>871939</v>
+        <v>871948</v>
       </c>
       <c r="R107" t="n">
-        <v>7441558</v>
+        <v>7441545</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11655,12 +11655,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11674,7 +11674,7 @@
         <v>126867221</v>
       </c>
       <c r="B108" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>126863364</v>
       </c>
       <c r="B109" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>126867222</v>
       </c>
       <c r="B110" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>126867204</v>
       </c>
       <c r="B111" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12099,45 +12099,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126867216</v>
+        <v>126867212</v>
       </c>
       <c r="B112" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>871704</v>
+        <v>871736</v>
       </c>
       <c r="R112" t="n">
-        <v>7441468</v>
+        <v>7441450</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12180,11 +12189,6 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Gammal gran</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12208,7 +12212,7 @@
         <v>126867206</v>
       </c>
       <c r="B113" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12311,10 +12315,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126863354</v>
+        <v>126867216</v>
       </c>
       <c r="B114" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12322,21 +12326,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12346,10 +12350,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>871850</v>
+        <v>871704</v>
       </c>
       <c r="R114" t="n">
-        <v>7441522</v>
+        <v>7441468</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12393,15 +12397,20 @@
       <c r="AG114" t="b">
         <v>0</v>
       </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Gammal gran</t>
+        </is>
+      </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12415,7 +12424,7 @@
         <v>126862986</v>
       </c>
       <c r="B115" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12514,54 +12523,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126867212</v>
+        <v>126863354</v>
       </c>
       <c r="B116" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>871736</v>
+        <v>871850</v>
       </c>
       <c r="R116" t="n">
-        <v>7441450</v>
+        <v>7441522</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12608,12 +12608,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12624,54 +12624,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126867215</v>
+        <v>126867223</v>
       </c>
       <c r="B117" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>871711</v>
+        <v>871614</v>
       </c>
       <c r="R117" t="n">
-        <v>7441464</v>
+        <v>7441544</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12714,6 +12705,11 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -12737,7 +12733,7 @@
         <v>126867210</v>
       </c>
       <c r="B118" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12844,45 +12840,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126867223</v>
+        <v>126867215</v>
       </c>
       <c r="B119" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>871614</v>
+        <v>871711</v>
       </c>
       <c r="R119" t="n">
-        <v>7441544</v>
+        <v>7441464</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12925,11 +12930,6 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -12950,54 +12950,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126867207</v>
+        <v>126863368</v>
       </c>
       <c r="B120" t="n">
-        <v>98361</v>
+        <v>82852</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>871895</v>
+        <v>871942</v>
       </c>
       <c r="R120" t="n">
-        <v>7441478</v>
+        <v>7441556</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13044,12 +13035,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13060,10 +13051,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126862992</v>
+        <v>126867207</v>
       </c>
       <c r="B121" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13088,17 +13079,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>871779</v>
+        <v>871895</v>
       </c>
       <c r="R121" t="n">
-        <v>7441493</v>
+        <v>7441478</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13145,12 +13145,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13161,32 +13161,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126863368</v>
+        <v>126862992</v>
       </c>
       <c r="B122" t="n">
-        <v>82792</v>
+        <v>98436</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13196,10 +13196,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>871942</v>
+        <v>871779</v>
       </c>
       <c r="R122" t="n">
-        <v>7441556</v>
+        <v>7441493</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13246,12 +13246,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13262,10 +13262,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126862993</v>
+        <v>126863366</v>
       </c>
       <c r="B123" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>871760</v>
+        <v>871942</v>
       </c>
       <c r="R123" t="n">
-        <v>7441560</v>
+        <v>7441556</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13347,12 +13347,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13363,10 +13363,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126863366</v>
+        <v>126862993</v>
       </c>
       <c r="B124" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13398,10 +13398,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>871942</v>
+        <v>871760</v>
       </c>
       <c r="R124" t="n">
-        <v>7441556</v>
+        <v>7441560</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13448,12 +13448,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13467,7 +13467,7 @@
         <v>126863350</v>
       </c>
       <c r="B125" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>126862990</v>
       </c>
       <c r="B126" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>126863359</v>
       </c>
       <c r="B127" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>126863357</v>
       </c>
       <c r="B128" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>126863351</v>
       </c>
       <c r="B129" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>126862995</v>
       </c>
       <c r="B130" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14070,10 +14070,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126863370</v>
+        <v>126862998</v>
       </c>
       <c r="B131" t="n">
-        <v>75067</v>
+        <v>82852</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14081,21 +14081,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14105,10 +14105,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>871721</v>
+        <v>871969</v>
       </c>
       <c r="R131" t="n">
-        <v>7441475</v>
+        <v>7441419</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14149,18 +14149,19 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14171,10 +14172,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126862997</v>
+        <v>126863000</v>
       </c>
       <c r="B132" t="n">
-        <v>78980</v>
+        <v>82852</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14182,21 +14183,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14206,10 +14207,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>871931</v>
+        <v>871964</v>
       </c>
       <c r="R132" t="n">
-        <v>7441549</v>
+        <v>7441492</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14250,6 +14251,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14272,10 +14274,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126863000</v>
+        <v>126863370</v>
       </c>
       <c r="B133" t="n">
-        <v>82792</v>
+        <v>75127</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14283,21 +14285,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14307,10 +14309,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>871964</v>
+        <v>871721</v>
       </c>
       <c r="R133" t="n">
-        <v>7441492</v>
+        <v>7441475</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14351,19 +14353,18 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14374,10 +14375,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126862998</v>
+        <v>126862997</v>
       </c>
       <c r="B134" t="n">
-        <v>82792</v>
+        <v>79011</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14385,21 +14386,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14409,10 +14410,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>871969</v>
+        <v>871931</v>
       </c>
       <c r="R134" t="n">
-        <v>7441419</v>
+        <v>7441549</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14453,7 +14454,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14476,54 +14476,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126867209</v>
+        <v>126862984</v>
       </c>
       <c r="B135" t="n">
-        <v>98361</v>
+        <v>75135</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>871768</v>
+        <v>871952</v>
       </c>
       <c r="R135" t="n">
-        <v>7441449</v>
+        <v>7441436</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14570,12 +14561,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Siri Borenberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14586,45 +14577,54 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126862984</v>
+        <v>126867209</v>
       </c>
       <c r="B136" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>871952</v>
+        <v>871768</v>
       </c>
       <c r="R136" t="n">
-        <v>7441436</v>
+        <v>7441449</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14671,12 +14671,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Siri Borenberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14690,7 +14690,7 @@
         <v>126863355</v>
       </c>
       <c r="B137" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>126867208</v>
       </c>
       <c r="B138" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14894,32 +14894,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126892197</v>
+        <v>126895285</v>
       </c>
       <c r="B139" t="n">
-        <v>75075</v>
+        <v>91330</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6440</v>
+        <v>1205</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14929,10 +14929,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>871956</v>
+        <v>871768</v>
       </c>
       <c r="R139" t="n">
-        <v>7441427</v>
+        <v>7441448</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14979,12 +14979,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126893383</v>
+        <v>126892197</v>
       </c>
       <c r="B140" t="n">
-        <v>79012</v>
+        <v>75135</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15006,21 +15006,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>871746</v>
+        <v>871956</v>
       </c>
       <c r="R140" t="n">
-        <v>7441444</v>
+        <v>7441427</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15080,12 +15080,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15096,32 +15096,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126895285</v>
+        <v>126893383</v>
       </c>
       <c r="B141" t="n">
-        <v>91256</v>
+        <v>79043</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1205</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15131,10 +15131,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>871768</v>
+        <v>871746</v>
       </c>
       <c r="R141" t="n">
-        <v>7441448</v>
+        <v>7441444</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15181,12 +15181,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
+          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Svea Nikula</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15301,7 +15301,7 @@
         <v>126892196</v>
       </c>
       <c r="B143" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>126895292</v>
       </c>
       <c r="B144" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15500,10 +15500,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126892892</v>
+        <v>126895278</v>
       </c>
       <c r="B145" t="n">
-        <v>77944</v>
+        <v>75135</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15511,21 +15511,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15535,10 +15535,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>871958</v>
+        <v>871862</v>
       </c>
       <c r="R145" t="n">
-        <v>7441471</v>
+        <v>7441413</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15585,12 +15585,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Svea Nikula, August Oljeqvist, Jonas Göransson, Amanda Rudelius</t>
+          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15601,10 +15601,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126895278</v>
+        <v>126892892</v>
       </c>
       <c r="B146" t="n">
-        <v>75075</v>
+        <v>78004</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15612,21 +15612,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15636,10 +15636,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>871862</v>
+        <v>871958</v>
       </c>
       <c r="R146" t="n">
-        <v>7441413</v>
+        <v>7441471</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15686,12 +15686,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
+          <t>Svea Nikula, August Oljeqvist, Jonas Göransson, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15705,7 +15705,7 @@
         <v>126895281</v>
       </c>
       <c r="B147" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>126895280</v>
       </c>
       <c r="B148" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15904,45 +15904,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126895286</v>
+        <v>126892893</v>
       </c>
       <c r="B149" t="n">
-        <v>98382</v>
+        <v>75135</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>871963</v>
+        <v>871961</v>
       </c>
       <c r="R149" t="n">
-        <v>7441548</v>
+        <v>7441512</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15983,18 +15986,19 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
+          <t>Svea Nikula, August Oljeqvist, Jonas Göransson, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -16005,48 +16009,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126892893</v>
+        <v>126895286</v>
       </c>
       <c r="B150" t="n">
-        <v>75075</v>
+        <v>98457</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>871961</v>
+        <v>871963</v>
       </c>
       <c r="R150" t="n">
-        <v>7441512</v>
+        <v>7441548</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16087,19 +16088,18 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Svea Nikula, August Oljeqvist, Jonas Göransson, Amanda Rudelius</t>
+          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16113,7 +16113,7 @@
         <v>126895291</v>
       </c>
       <c r="B151" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>126895297</v>
       </c>
       <c r="B152" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>126895279</v>
       </c>
       <c r="B153" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>126893387</v>
       </c>
       <c r="B154" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>126892194</v>
       </c>
       <c r="B156" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>126892195</v>
       </c>
       <c r="B157" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16827,10 +16827,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126893390</v>
+        <v>126895295</v>
       </c>
       <c r="B158" t="n">
-        <v>77934</v>
+        <v>79011</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16838,37 +16838,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>871955</v>
+        <v>871954</v>
       </c>
       <c r="R158" t="n">
-        <v>7441488</v>
+        <v>7441541</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16903,21 +16900,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Mikroskoperad av Linnea Ingelsbo</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -16925,12 +16912,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist, Amanda Rudelius, Svea Nikula</t>
+          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16944,7 +16931,7 @@
         <v>126892894</v>
       </c>
       <c r="B159" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17043,10 +17030,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126895295</v>
+        <v>126893390</v>
       </c>
       <c r="B160" t="n">
-        <v>78980</v>
+        <v>77994</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17054,34 +17041,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Aapua, Nb</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>871954</v>
+        <v>871955</v>
       </c>
       <c r="R160" t="n">
-        <v>7441541</v>
+        <v>7441488</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17116,11 +17106,21 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Mikroskoperad av Linnea Ingelsbo</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -17128,12 +17128,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson, Svea Nikula, Amanda Rudelius</t>
+          <t>Jonas Göransson, August Oljeqvist, Amanda Rudelius, Svea Nikula</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
